--- a/data/trans_dic/P32E$amigos_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32E$amigos_2023-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -577,12 +577,12 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,82; 59,48</t>
+          <t>6,73; 59,75</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,76; 50,25</t>
+          <t>11,17; 49,43</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>22,16; 72,09</t>
+          <t>18,6; 71,69</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,28; 69,61</t>
+          <t>10,03; 69,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>25,14; 63,41</t>
+          <t>23,53; 63,18</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,33; 38,95</t>
+          <t>7,52; 39,0</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,27; 33,33</t>
+          <t>6,35; 33,17</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 38,53</t>
+          <t>7,12; 38,6</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,89; 49,05</t>
+          <t>1,96; 49,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,01; 32,12</t>
+          <t>7,81; 30,3</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,48; 30,26</t>
+          <t>3,41; 28,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 45,65</t>
+          <t>0,0; 41,27</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,23; 26,38</t>
+          <t>3,25; 25,28</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6,21; 45,43</t>
+          <t>5,98; 46,13</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,14</t>
+          <t>0,0; 62,07</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,44; 39,4</t>
+          <t>7,86; 41,07</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 20,75</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>16,21; 33,2</t>
+          <t>15,84; 32,6</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,36; 36,29</t>
+          <t>9,91; 34,48</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,66; 30,61</t>
+          <t>16,39; 29,47</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en casa de amistades/familiares (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1088,12 +1088,12 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>894; 9131</t>
+          <t>1033; 9173</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4820; 20601</t>
+          <t>4581; 20264</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>5089; 16554</t>
+          <t>4272; 16463</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1392; 9425</t>
+          <t>1358; 9363</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>9178; 23148</t>
+          <t>8588; 23064</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1969; 10459</t>
+          <t>2020; 10475</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 1132</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2025; 10770</t>
+          <t>2051; 10718</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1952; 10629</t>
+          <t>1965; 10651</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>171; 4433</t>
+          <t>177; 4455</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2935; 11765</t>
+          <t>2859; 11097</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>790; 6875</t>
+          <t>775; 6537</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2793</t>
+          <t>0; 2524</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>933; 7606</t>
+          <t>937; 7290</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>823; 6019</t>
+          <t>793; 6111</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2161</t>
+          <t>0; 2159</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1244; 6590</t>
+          <t>1315; 6870</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1056</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 989</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1166</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>23355; 47840</t>
+          <t>22821; 46973</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>6761; 19857</t>
+          <t>5425; 18865</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>33115; 60859</t>
+          <t>32587; 58588</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$amigos_2023-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P32E$amigos_2023-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>33,11%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>34,08%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7,31; 60,68</t>
+          <t>10,38; 66,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>6,73; 59,75</t>
+          <t>10,09; 65,01</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,17; 49,43</t>
+          <t>17,12; 56,98</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>40,11%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>38,13%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>37,9%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>18,6; 71,69</t>
+          <t>16,45; 66,03</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>10,03; 69,15</t>
+          <t>7,69; 63,84</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23,53; 63,18</t>
+          <t>21,45; 58,04</t>
         </is>
       </c>
     </row>
@@ -649,7 +649,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>18,87%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -659,7 +659,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>16,26%</t>
+          <t>15,44%</t>
         </is>
       </c>
     </row>
@@ -672,7 +672,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,52; 39,0</t>
+          <t>7,19; 37,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -682,7 +682,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,35; 33,17</t>
+          <t>5,69; 30,34</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>16,79%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,43%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>7,12; 38,6</t>
+          <t>6,33; 34,15</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,96; 49,3</t>
+          <t>5,98; 45,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,81; 30,3</t>
+          <t>7,71; 32,01</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,22%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,41; 28,77</t>
+          <t>3,48; 28,84</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,27</t>
+          <t>0,0; 42,9</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,25; 25,28</t>
+          <t>3,1; 26,38</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>21,74%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>21,6%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>5,98; 46,13</t>
+          <t>6,38; 47,51</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 62,07</t>
+          <t>0,0; 63,78</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>7,86; 41,07</t>
+          <t>8,35; 43,09</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>22,72%</t>
+          <t>23,45%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>15,84; 32,6</t>
+          <t>16,03; 33,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>9,91; 34,48</t>
+          <t>12,97; 36,35</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>16,39; 29,47</t>
+          <t>17,31; 31,07</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>10246</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>3917</t>
+          <t>5947</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11078</t>
+          <t>16193</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1874; 15561</t>
+          <t>3067; 19566</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1033; 9173</t>
+          <t>1812; 11676</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4581; 20264</t>
+          <t>8134; 27072</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>10479</t>
+          <t>11201</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>5163</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>15642</t>
+          <t>16637</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>4272; 16463</t>
+          <t>4594; 18438</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1358; 9363</t>
+          <t>1228; 10197</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8588; 23064</t>
+          <t>9417; 25478</t>
         </is>
       </c>
     </row>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5601</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5253</t>
+          <t>5601</t>
         </is>
       </c>
     </row>
@@ -1229,7 +1229,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2020; 10475</t>
+          <t>2134; 11072</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1239,7 +1239,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2051; 10718</t>
+          <t>2063; 11006</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>5020</t>
+          <t>5117</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>1480</t>
+          <t>2063</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6500</t>
+          <t>7180</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1965; 10651</t>
+          <t>1929; 10403</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>177; 4455</t>
+          <t>642; 4934</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2859; 11097</t>
+          <t>3177; 13190</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>2634</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>631</t>
+          <t>727</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3273</t>
+          <t>3361</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>775; 6537</t>
+          <t>808; 6703</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0; 2524</t>
+          <t>0; 2879</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>937; 7290</t>
+          <t>929; 7902</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>2881</t>
+          <t>3348</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>541</t>
+          <t>608</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>3422</t>
+          <t>3957</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>793; 6111</t>
+          <t>923; 6875</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 2159</t>
+          <t>0; 2454</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1315; 6870</t>
+          <t>1529; 7893</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>33436</t>
+          <t>38147</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>11733</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>45169</t>
+          <t>52929</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>22821; 46973</t>
+          <t>25878; 53549</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>5425; 18865</t>
+          <t>8327; 23332</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>32587; 58588</t>
+          <t>39074; 70110</t>
         </is>
       </c>
     </row>
